--- a/data/CONTROLE - VEXPENSES - JULHO 2026 - 2QZ - API.xlsx
+++ b/data/CONTROLE - VEXPENSES - JULHO 2026 - 2QZ - API.xlsx
@@ -849,7 +849,7 @@
         <v>-35</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>-3293.85</v>
+        <v>-3293.849999999999</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>-1707.81</v>
@@ -1104,7 +1104,7 @@
         <v>-119</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-6594.63</v>
+        <v>-6594.629999999999</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>642</v>
@@ -2011,7 +2011,7 @@
         <v>-49</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>-8963.690000000001</v>
+        <v>-8963.689999999999</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>217.12</v>
@@ -4641,7 +4641,7 @@
         <v>-28</v>
       </c>
       <c r="Q60" s="3" t="n">
-        <v>-7749.87</v>
+        <v>-7749.869999999999</v>
       </c>
       <c r="R60" s="3" t="n">
         <v>0.2</v>
@@ -5038,16 +5038,16 @@
         <v>0</v>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>-798.6</v>
+        <v>-269.52</v>
       </c>
       <c r="R65" s="3" t="n">
-        <v>-798.6</v>
+        <v>-269.52</v>
       </c>
       <c r="S65" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T65" s="3" t="n">
-        <v>-798.6</v>
+        <v>-269.52</v>
       </c>
       <c r="U65" s="3" t="inlineStr"/>
       <c r="V65" s="3" t="n">
@@ -5206,16 +5206,16 @@
         <v>-7</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>-3154.12</v>
+        <v>-1755.45</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>-2364.12</v>
+        <v>-965.45</v>
       </c>
       <c r="S67" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>-2364.12</v>
+        <v>-965.45</v>
       </c>
       <c r="U67" s="3" t="inlineStr"/>
       <c r="V67" s="3" t="inlineStr"/>
@@ -6526,7 +6526,7 @@
         <v>-553.25</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>-68761.73</v>
+        <v>-68761.73000000001</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>2576.15</v>
@@ -7488,7 +7488,7 @@
         <v>-217</v>
       </c>
       <c r="Q95" s="3" t="n">
-        <v>-35338.36</v>
+        <v>-35338.35999999999</v>
       </c>
       <c r="R95" s="3" t="n">
         <v>7737.22</v>
@@ -9217,16 +9217,16 @@
         <v>-0</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>-844.2</v>
+        <v>-240.2</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>55.8</v>
+        <v>659.8</v>
       </c>
       <c r="S116" s="3" t="n">
         <v>-900</v>
       </c>
       <c r="T116" s="3" t="n">
-        <v>-844.2</v>
+        <v>-240.2</v>
       </c>
       <c r="U116" s="3" t="inlineStr"/>
       <c r="V116" s="3" t="n">
@@ -9385,7 +9385,7 @@
         <v>-700</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>-54219.85</v>
+        <v>-54219.85000000001</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>42729.55</v>
@@ -12384,7 +12384,7 @@
         <v>-21</v>
       </c>
       <c r="Q155" s="3" t="n">
-        <v>-850.45</v>
+        <v>-850.4499999999999</v>
       </c>
       <c r="R155" s="3" t="n">
         <v>-39.35</v>
@@ -12712,7 +12712,7 @@
         <v>-56</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>-7503.95</v>
+        <v>-7503.950000000001</v>
       </c>
       <c r="R159" s="3" t="n">
         <v>-1663.95</v>
@@ -13925,16 +13925,16 @@
         <v>-147</v>
       </c>
       <c r="Q174" s="3" t="n">
-        <v>-15043.43</v>
+        <v>-15406.03</v>
       </c>
       <c r="R174" s="3" t="n">
-        <v>1488.82</v>
+        <v>1126.22</v>
       </c>
       <c r="S174" s="3" t="n">
         <v>-182.25</v>
       </c>
       <c r="T174" s="3" t="n">
-        <v>1306.57</v>
+        <v>943.97</v>
       </c>
       <c r="U174" s="3" t="inlineStr"/>
       <c r="V174" s="3" t="n">
@@ -14597,7 +14597,7 @@
         <v>-399</v>
       </c>
       <c r="Q182" s="3" t="n">
-        <v>-44267.74</v>
+        <v>-44267.74000000001</v>
       </c>
       <c r="R182" s="3" t="n">
         <v>-609.29</v>
@@ -14682,7 +14682,7 @@
         <v>-0</v>
       </c>
       <c r="Q183" s="3" t="n">
-        <v>-2210.22</v>
+        <v>-2210.219999999999</v>
       </c>
       <c r="R183" s="3" t="n">
         <v>13.81</v>
@@ -16040,7 +16040,7 @@
         <v>-63</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>-7054.74</v>
+        <v>-7054.739999999999</v>
       </c>
       <c r="R199" s="3" t="n">
         <v>1436.8</v>
@@ -18406,16 +18406,16 @@
         <v>-14</v>
       </c>
       <c r="Q227" s="3" t="n">
-        <v>-844.67</v>
+        <v>-909.67</v>
       </c>
       <c r="R227" s="3" t="n">
-        <v>108.29</v>
+        <v>43.29</v>
       </c>
       <c r="S227" s="3" t="n">
         <v>-168</v>
       </c>
       <c r="T227" s="3" t="n">
-        <v>-59.71</v>
+        <v>-124.71</v>
       </c>
       <c r="U227" s="3" t="inlineStr"/>
       <c r="V227" s="3" t="n">
@@ -19789,7 +19789,7 @@
         <v>-364</v>
       </c>
       <c r="Q244" s="3" t="n">
-        <v>-47446.36</v>
+        <v>-47446.35999999999</v>
       </c>
       <c r="R244" s="3" t="n">
         <v>-853.0599999999999</v>
@@ -21048,7 +21048,7 @@
         <v>-441.5</v>
       </c>
       <c r="Q259" s="3" t="n">
-        <v>-58215.97</v>
+        <v>-58215.97000000001</v>
       </c>
       <c r="R259" s="3" t="n">
         <v>-2559.3</v>
@@ -21896,7 +21896,7 @@
         <v>-441</v>
       </c>
       <c r="Q269" s="3" t="n">
-        <v>-50392.19</v>
+        <v>-50392.19000000001</v>
       </c>
       <c r="R269" s="3" t="n">
         <v>1186.35</v>
@@ -23711,7 +23711,7 @@
         <v>-292.41</v>
       </c>
       <c r="Q292" s="3" t="n">
-        <v>-36569.28</v>
+        <v>-36569.27999999999</v>
       </c>
       <c r="R292" s="3" t="n">
         <v>-4615.94</v>
@@ -24673,7 +24673,7 @@
         <v>-378</v>
       </c>
       <c r="Q304" s="3" t="n">
-        <v>-54922.39</v>
+        <v>-54922.38999999999</v>
       </c>
       <c r="R304" s="3" t="n">
         <v>3322.54</v>
@@ -26084,7 +26084,7 @@
         <v>-35</v>
       </c>
       <c r="Q321" s="3" t="n">
-        <v>-4050.57</v>
+        <v>-4050.570000000001</v>
       </c>
       <c r="R321" s="3" t="n">
         <v>495.81</v>
@@ -26926,16 +26926,16 @@
         <v>-133</v>
       </c>
       <c r="Q331" s="3" t="n">
-        <v>-6402.22</v>
+        <v>-7552.22</v>
       </c>
       <c r="R331" s="3" t="n">
-        <v>-1053.93</v>
+        <v>-2203.93</v>
       </c>
       <c r="S331" s="3" t="n">
         <v>-3</v>
       </c>
       <c r="T331" s="3" t="n">
-        <v>-1056.93</v>
+        <v>-2206.93</v>
       </c>
       <c r="U331" s="3" t="inlineStr"/>
       <c r="V331" s="3" t="n">
@@ -27902,7 +27902,7 @@
         <v>-28</v>
       </c>
       <c r="Q343" s="3" t="n">
-        <v>-7602.4</v>
+        <v>-7602.400000000001</v>
       </c>
       <c r="R343" s="3" t="n">
         <v>-3530.32</v>
@@ -28692,7 +28692,7 @@
         <v>-301</v>
       </c>
       <c r="Q353" s="3" t="n">
-        <v>-39432.03</v>
+        <v>-39432.03000000001</v>
       </c>
       <c r="R353" s="3" t="n">
         <v>-561.36</v>
@@ -30526,16 +30526,16 @@
         <v>-63.31</v>
       </c>
       <c r="Q375" s="3" t="n">
-        <v>-3459.8</v>
+        <v>-3491.6</v>
       </c>
       <c r="R375" s="3" t="n">
-        <v>182</v>
+        <v>150.2</v>
       </c>
       <c r="S375" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="T375" s="3" t="n">
-        <v>182</v>
+        <v>150.2</v>
       </c>
       <c r="U375" s="3" t="inlineStr"/>
       <c r="V375" s="3" t="inlineStr"/>
@@ -31748,16 +31748,16 @@
         <v>-0</v>
       </c>
       <c r="Q391" s="3" t="n">
-        <v>-12556.79</v>
+        <v>-12736.79</v>
       </c>
       <c r="R391" s="3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="S391" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="T391" s="3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="U391" s="3" t="inlineStr"/>
       <c r="V391" s="3" t="n">
@@ -33285,7 +33285,7 @@
         <v>-462.77</v>
       </c>
       <c r="Q410" s="3" t="n">
-        <v>-58288.58</v>
+        <v>-58288.58000000001</v>
       </c>
       <c r="R410" s="3" t="n">
         <v>1602.24</v>
@@ -34131,7 +34131,7 @@
         <v>-113.58</v>
       </c>
       <c r="Q420" s="3" t="n">
-        <v>-6094.87</v>
+        <v>-6094.869999999999</v>
       </c>
       <c r="R420" s="3" t="n">
         <v>-164.56</v>
@@ -34724,7 +34724,7 @@
         <v>-84</v>
       </c>
       <c r="Q427" s="3" t="n">
-        <v>-5971.42</v>
+        <v>-5971.420000000001</v>
       </c>
       <c r="R427" s="3" t="n">
         <v>485.1</v>
@@ -34977,7 +34977,7 @@
         <v>-280</v>
       </c>
       <c r="Q430" s="3" t="n">
-        <v>-31622.63</v>
+        <v>-31622.62999999999</v>
       </c>
       <c r="R430" s="3" t="n">
         <v>-2907.87</v>
@@ -36279,7 +36279,7 @@
         <v>-84.16</v>
       </c>
       <c r="Q446" s="3" t="n">
-        <v>-5523.31</v>
+        <v>-5523.309999999999</v>
       </c>
       <c r="R446" s="3" t="n">
         <v>267.62</v>
@@ -36364,7 +36364,7 @@
         <v>-14</v>
       </c>
       <c r="Q447" s="3" t="n">
-        <v>-9593.33</v>
+        <v>-9593.330000000002</v>
       </c>
       <c r="R447" s="3" t="n">
         <v>350</v>
@@ -36840,7 +36840,7 @@
         <v>-17.96</v>
       </c>
       <c r="Q453" s="3" t="n">
-        <v>-8560.379999999999</v>
+        <v>-8560.380000000001</v>
       </c>
       <c r="R453" s="3" t="n">
         <v>944.14</v>
@@ -37763,7 +37763,7 @@
         <v>-42</v>
       </c>
       <c r="Q464" s="3" t="n">
-        <v>-5529.96</v>
+        <v>-5529.959999999999</v>
       </c>
       <c r="R464" s="3" t="n">
         <v>5931.36</v>
@@ -42246,7 +42246,7 @@
         <v>-357</v>
       </c>
       <c r="Q517" s="3" t="n">
-        <v>-81179.85000000001</v>
+        <v>-81179.84999999999</v>
       </c>
       <c r="R517" s="3" t="n">
         <v>2022.76</v>
@@ -43149,16 +43149,16 @@
         <v>-98</v>
       </c>
       <c r="Q528" s="3" t="n">
-        <v>-8404.1</v>
+        <v>-8552.800000000001</v>
       </c>
       <c r="R528" s="3" t="n">
-        <v>826.2</v>
+        <v>677.5</v>
       </c>
       <c r="S528" s="3" t="n">
         <v>-0.3</v>
       </c>
       <c r="T528" s="3" t="n">
-        <v>825.9</v>
+        <v>677.2</v>
       </c>
       <c r="U528" s="3" t="inlineStr"/>
       <c r="V528" s="3" t="n">
@@ -44222,7 +44222,7 @@
         <v>-70</v>
       </c>
       <c r="Q541" s="3" t="n">
-        <v>-6208.42</v>
+        <v>-6208.419999999999</v>
       </c>
       <c r="R541" s="3" t="n">
         <v>756.04</v>
@@ -49026,7 +49026,7 @@
         <v>-35</v>
       </c>
       <c r="Q599" s="3" t="n">
-        <v>-680.4</v>
+        <v>-680.4000000000001</v>
       </c>
       <c r="R599" s="3" t="n">
         <v>247.4</v>
@@ -49530,7 +49530,7 @@
         <v>-28</v>
       </c>
       <c r="Q605" s="3" t="n">
-        <v>-4150.61</v>
+        <v>-4150.610000000001</v>
       </c>
       <c r="R605" s="3" t="n">
         <v>463.99</v>
@@ -50662,16 +50662,16 @@
         <v>0</v>
       </c>
       <c r="Q619" s="3" t="n">
-        <v>-95.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="R619" s="3" t="n">
-        <v>-95.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="S619" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T619" s="3" t="n">
-        <v>-95.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="U619" s="3" t="inlineStr"/>
       <c r="V619" s="3" t="inlineStr"/>
@@ -51166,16 +51166,16 @@
         <v>-70</v>
       </c>
       <c r="Q625" s="3" t="n">
-        <v>-29064.52</v>
+        <v>-18680.82</v>
       </c>
       <c r="R625" s="3" t="n">
-        <v>-12062.79</v>
+        <v>-1679.09</v>
       </c>
       <c r="S625" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="T625" s="3" t="n">
-        <v>-12062.79</v>
+        <v>-1679.09</v>
       </c>
       <c r="U625" s="3" t="inlineStr"/>
       <c r="V625" s="3" t="inlineStr"/>
@@ -52575,7 +52575,7 @@
         <v>-98</v>
       </c>
       <c r="Q642" s="3" t="n">
-        <v>-8283.82</v>
+        <v>-8283.820000000002</v>
       </c>
       <c r="R642" s="3" t="n">
         <v>618.3</v>
@@ -52719,7 +52719,7 @@
         <v>-32.54</v>
       </c>
       <c r="Q644" s="3" t="n">
-        <v>-5282.86</v>
+        <v>-5282.859999999999</v>
       </c>
       <c r="R644" s="3" t="n">
         <v>203.18</v>
@@ -53031,16 +53031,16 @@
         <v>-7</v>
       </c>
       <c r="Q648" s="3" t="n">
-        <v>-10042.36</v>
+        <v>-10716.18</v>
       </c>
       <c r="R648" s="3" t="n">
-        <v>156.1</v>
+        <v>-517.72</v>
       </c>
       <c r="S648" s="3" t="n">
         <v>-436.1</v>
       </c>
       <c r="T648" s="3" t="n">
-        <v>-280</v>
+        <v>-953.8200000000001</v>
       </c>
       <c r="U648" s="3" t="inlineStr"/>
       <c r="V648" s="3" t="n">
@@ -54418,7 +54418,7 @@
         <v>-63</v>
       </c>
       <c r="Q665" s="3" t="n">
-        <v>-6728.46</v>
+        <v>-6728.459999999999</v>
       </c>
       <c r="R665" s="3" t="n">
         <v>100.38</v>
@@ -55519,16 +55519,16 @@
         <v>-21</v>
       </c>
       <c r="Q678" s="3" t="n">
-        <v>-3811.93</v>
+        <v>-3881.93</v>
       </c>
       <c r="R678" s="3" t="n">
-        <v>401.63</v>
+        <v>331.63</v>
       </c>
       <c r="S678" s="3" t="n">
         <v>-160</v>
       </c>
       <c r="T678" s="3" t="n">
-        <v>241.63</v>
+        <v>171.63</v>
       </c>
       <c r="U678" s="3" t="inlineStr"/>
       <c r="V678" s="3" t="n">
@@ -55604,7 +55604,7 @@
         <v>-0</v>
       </c>
       <c r="Q679" s="3" t="n">
-        <v>-937.53</v>
+        <v>-937.5300000000001</v>
       </c>
       <c r="R679" s="3" t="n">
         <v>182.67</v>
@@ -56025,7 +56025,7 @@
         <v>-21</v>
       </c>
       <c r="Q684" s="3" t="n">
-        <v>-969.6</v>
+        <v>-969.5999999999999</v>
       </c>
       <c r="R684" s="3" t="n">
         <v>410.4</v>
@@ -56274,7 +56274,7 @@
         <v>-7</v>
       </c>
       <c r="Q687" s="3" t="n">
-        <v>-3956.35</v>
+        <v>-3956.349999999999</v>
       </c>
       <c r="R687" s="3" t="n">
         <v>1.18</v>
@@ -58025,16 +58025,16 @@
         <v>-182</v>
       </c>
       <c r="Q708" s="3" t="n">
-        <v>-23494.28</v>
+        <v>-23699.28</v>
       </c>
       <c r="R708" s="3" t="n">
-        <v>-1288.15</v>
+        <v>-1493.15</v>
       </c>
       <c r="S708" s="3" t="n">
         <v>-340.06</v>
       </c>
       <c r="T708" s="3" t="n">
-        <v>-1628.21</v>
+        <v>-1833.21</v>
       </c>
       <c r="U708" s="3" t="inlineStr"/>
       <c r="V708" s="3" t="n">
@@ -58608,16 +58608,16 @@
         <v>-214.35</v>
       </c>
       <c r="Q715" s="3" t="n">
-        <v>-46626.32</v>
+        <v>-47106.32</v>
       </c>
       <c r="R715" s="3" t="n">
-        <v>4207</v>
+        <v>3727</v>
       </c>
       <c r="S715" s="3" t="n">
         <v>-292.54</v>
       </c>
       <c r="T715" s="3" t="n">
-        <v>3914.46</v>
+        <v>3434.46</v>
       </c>
       <c r="U715" s="3" t="inlineStr"/>
       <c r="V715" s="3" t="n">
@@ -58946,7 +58946,7 @@
         <v>-539</v>
       </c>
       <c r="Q719" s="3" t="n">
-        <v>-64494.57</v>
+        <v>-64494.57000000001</v>
       </c>
       <c r="R719" s="3" t="n">
         <v>3192.91</v>
@@ -60752,7 +60752,7 @@
         <v>-161</v>
       </c>
       <c r="Q741" s="3" t="n">
-        <v>-8124.33</v>
+        <v>-8124.330000000001</v>
       </c>
       <c r="R741" s="3" t="n">
         <v>1500</v>
@@ -61090,16 +61090,16 @@
         <v>-437</v>
       </c>
       <c r="Q745" s="3" t="n">
-        <v>-44644.78</v>
+        <v>-45642.68</v>
       </c>
       <c r="R745" s="3" t="n">
-        <v>529.47</v>
+        <v>-468.43</v>
       </c>
       <c r="S745" s="3" t="n">
         <v>-14.25</v>
       </c>
       <c r="T745" s="3" t="n">
-        <v>515.22</v>
+        <v>-482.68</v>
       </c>
       <c r="U745" s="3" t="inlineStr"/>
       <c r="V745" s="3" t="n">
@@ -61430,16 +61430,16 @@
         <v>-195.91</v>
       </c>
       <c r="Q749" s="3" t="n">
-        <v>-10631.72</v>
+        <v>-10868.52</v>
       </c>
       <c r="R749" s="3" t="n">
-        <v>2169.74</v>
+        <v>1932.94</v>
       </c>
       <c r="S749" s="3" t="n">
         <v>-0.88</v>
       </c>
       <c r="T749" s="3" t="n">
-        <v>2168.86</v>
+        <v>1932.06</v>
       </c>
       <c r="U749" s="3" t="inlineStr"/>
       <c r="V749" s="3" t="n">
@@ -63912,7 +63912,7 @@
         <v>-518</v>
       </c>
       <c r="Q779" s="3" t="n">
-        <v>-60327.65</v>
+        <v>-60327.65000000001</v>
       </c>
       <c r="R779" s="3" t="n">
         <v>3560.48</v>
@@ -65042,7 +65042,7 @@
         <v>-245</v>
       </c>
       <c r="Q793" s="3" t="n">
-        <v>-28298.85</v>
+        <v>-28298.84999999999</v>
       </c>
       <c r="R793" s="3" t="n">
         <v>1390</v>
@@ -65716,7 +65716,7 @@
         <v>-385</v>
       </c>
       <c r="Q801" s="3" t="n">
-        <v>-39475.43</v>
+        <v>-39475.42999999999</v>
       </c>
       <c r="R801" s="3" t="n">
         <v>4883</v>
@@ -66054,7 +66054,7 @@
         <v>-0</v>
       </c>
       <c r="Q805" s="3" t="n">
-        <v>-4351.19</v>
+        <v>-4351.190000000001</v>
       </c>
       <c r="R805" s="3" t="n">
         <v>500</v>
